--- a/descriptive tables/desc_remittance.xlsx
+++ b/descriptive tables/desc_remittance.xlsx
@@ -22,10 +22,10 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="5">
   <si>
-    <t xml:space="preserve">variable</t>
+    <t xml:space="preserve">province</t>
   </si>
   <si>
-    <t xml:space="preserve">province</t>
+    <t xml:space="preserve">variable</t>
   </si>
   <si>
     <t xml:space="preserve">mean_value</t>
@@ -312,10 +312,10 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr defaultColWidth="10.59765625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="10.6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="16.79"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -325,163 +325,173 @@
       <c r="B1" s="0" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="0" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="0" t="n">
+      <c r="A2" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="B2" s="0" t="s">
+        <v>3</v>
+      </c>
       <c r="C2" s="1" t="n">
-        <v>346821.471774194</v>
+        <v>324687.239583333</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="0" t="n">
+      <c r="A3" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="B3" s="0" t="s">
+        <v>4</v>
+      </c>
       <c r="C3" s="1" t="n">
-        <v>181590.725806452</v>
+        <v>164262.152777778</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="0" t="n">
+      <c r="A4" s="0" t="n">
         <v>2</v>
       </c>
+      <c r="B4" s="0" t="s">
+        <v>3</v>
+      </c>
       <c r="C4" s="1" t="n">
-        <v>264670.365296804</v>
+        <v>261956.068111455</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" s="0" t="n">
+      <c r="A5" s="0" t="n">
         <v>2</v>
       </c>
+      <c r="B5" s="0" t="s">
+        <v>4</v>
+      </c>
       <c r="C5" s="1" t="n">
-        <v>99170.2511415525</v>
+        <v>101397.786377709</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" s="0" t="n">
+      <c r="A6" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" s="0" t="s">
         <v>3</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>301716.702631579</v>
+        <v>262545.099818512</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="B7" s="0" t="n">
-        <v>3</v>
+      <c r="A7" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="0" t="s">
+        <v>4</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>111600.263157895</v>
+        <v>92254.2649727768</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="B8" s="0" t="n">
-        <v>4</v>
+      <c r="A8" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="0" t="s">
+        <v>3</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>418462.333333333</v>
+        <v>426858.52233677</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="B9" s="0" t="n">
+      <c r="A9" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="B9" s="0" t="s">
         <v>4</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>74916.6962962963</v>
-      </c>
+        <v>70549.8556701031</v>
+      </c>
+      <c r="E9" s="1"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="B10" s="0" t="n">
+      <c r="A10" s="0" t="n">
         <v>5</v>
       </c>
+      <c r="B10" s="0" t="s">
+        <v>3</v>
+      </c>
       <c r="C10" s="1" t="n">
-        <v>347396.432432432</v>
-      </c>
+        <v>355386.012738854</v>
+      </c>
+      <c r="E10" s="1"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="B11" s="0" t="n">
+      <c r="A11" s="0" t="n">
         <v>5</v>
       </c>
+      <c r="B11" s="0" t="s">
+        <v>4</v>
+      </c>
       <c r="C11" s="1" t="n">
-        <v>86855.8558558559</v>
-      </c>
+        <v>87564.6496815287</v>
+      </c>
+      <c r="E11" s="1"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="B12" s="0" t="n">
+      <c r="A12" s="0" t="n">
         <v>6</v>
       </c>
+      <c r="B12" s="0" t="s">
+        <v>3</v>
+      </c>
       <c r="C12" s="1" t="n">
-        <v>140568.640718563</v>
-      </c>
+        <v>140287.557017544</v>
+      </c>
+      <c r="E12" s="1"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="B13" s="0" t="n">
+      <c r="A13" s="0" t="n">
         <v>6</v>
       </c>
+      <c r="B13" s="0" t="s">
+        <v>4</v>
+      </c>
       <c r="C13" s="1" t="n">
-        <v>180901.19760479</v>
-      </c>
+        <v>178006.140350877</v>
+      </c>
+      <c r="E13" s="1"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="B14" s="0" t="n">
+      <c r="A14" s="0" t="n">
         <v>7</v>
       </c>
+      <c r="B14" s="0" t="s">
+        <v>3</v>
+      </c>
       <c r="C14" s="1" t="n">
-        <v>164647.247191011</v>
-      </c>
+        <v>137619.733606557</v>
+      </c>
+      <c r="E14" s="1"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="B15" s="0" t="n">
+      <c r="A15" s="0" t="n">
         <v>7</v>
       </c>
+      <c r="B15" s="0" t="s">
+        <v>4</v>
+      </c>
       <c r="C15" s="1" t="n">
-        <v>62218.2584269663</v>
-      </c>
+        <v>70190.7786885246</v>
+      </c>
+      <c r="E15" s="1"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E16" s="1"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
